--- a/media/report_releases/daily/report-releases-2026-10-30.xlsx
+++ b/media/report_releases/daily/report-releases-2026-10-30.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Report Releases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Report Releases'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Report Releases'!$A$1:$L$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,8 +21,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="167" formatCode="dd-mmm-yyyy hh:mm:ss AM/PM"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy hh:mm:ss AM/PM"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -84,7 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -452,19 +455,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -480,40 +485,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Analysis End Date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Previous Analysis End Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Released On (Date &amp; Time)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Certificate No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Batch No</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Booking ID</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Sample Name</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Party</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Released By</t>
         </is>
@@ -524,42 +539,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>46127</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
         <v>46325.51828599506</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>ARL/GEN/260416002</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>LB6181</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Zenith Drugs Ltd</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
@@ -570,42 +589,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>46127</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="4" t="n">
         <v>46325.51862217351</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>ARL/GEN/260416002</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>LB6181</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Zenith Drugs Ltd</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
@@ -616,42 +639,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>46127</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
         <v>46325.51867574637</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>ARL/GEN/260416002</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>LB6181</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Zenith Drugs Ltd</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
@@ -662,42 +689,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>46127</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
         <v>46325.53781896829</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>ARL/GEN/260416002</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>LB6181</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Zenith Drugs Ltd</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
@@ -708,42 +739,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>46125</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="4" t="n">
         <v>46325.53875281198</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>ARL/GEN/260416001</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>goufoyf</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Compund</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
@@ -754,42 +789,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>46127</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="4" t="n">
         <v>46325.54012793327</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>ARL/GEN/260416002</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>LB6181</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Zenith Drugs Ltd</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
@@ -799,41 +838,45 @@
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="6" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="7" t="n">
         <v>46325.54400168856</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>ARL/GEN/260416021</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>LB6181</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Zenith Drugs Ltd</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
@@ -844,49 +887,203 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>46118</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="4" t="n">
         <v>46325.55584627139</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>ARL/GEN/260416021</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>LB6181</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Zenith Drugs Ltd</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="4" t="n">
+        <v>46325.61537881845</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ARL/GEN/260416015</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>LB6181</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Zenith Drugs Ltd</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="7" t="n">
+        <v>46325.74263949904</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ARL/GEN/260416008</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>LB6181</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Zenith Drugs Ltd</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="4" t="n">
+        <v>46325.74599003191</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ARL/GEN/260416008</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>LB6181</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Calcizen Suspension (Calcium Phosphate Vitamin D3 &amp; B12 Suspension)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Zenith Drugs Ltd</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:L12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>